--- a/dist/Stellantis-Cost-Intelligence/_internal/dados/TC_Principal/Forecast/df_vol_historico.xlsx
+++ b/dist/Stellantis-Cost-Intelligence/_internal/dados/TC_Principal/Forecast/df_vol_historico.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="D14" t="n">
         <v>2026</v>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1526</v>
+        <v>1365</v>
       </c>
       <c r="D15" t="n">
         <v>2026</v>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D16" t="n">
         <v>2026</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D17" t="n">
         <v>2026</v>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
         <v>2026</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="D19" t="n">
         <v>2026</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="D20" t="n">
         <v>2026</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="D21" t="n">
         <v>2026</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="D24" t="n">
         <v>2026</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1958</v>
+        <v>2196</v>
       </c>
       <c r="D25" t="n">
         <v>2026</v>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D26" t="n">
         <v>2026</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="D27" t="n">
         <v>2026</v>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="D28" t="n">
         <v>2026</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="D29" t="n">
         <v>2026</v>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="D30" t="n">
         <v>2026</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1464</v>
+        <v>1540</v>
       </c>
       <c r="D31" t="n">
         <v>2026</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="D34" t="n">
         <v>2026</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1676</v>
+        <v>1944</v>
       </c>
       <c r="D35" t="n">
         <v>2026</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D36" t="n">
         <v>2026</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="D37" t="n">
         <v>2026</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="D38" t="n">
         <v>2026</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>173</v>
+        <v>524</v>
       </c>
       <c r="D39" t="n">
         <v>2026</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D40" t="n">
         <v>2026</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1368</v>
+        <v>1351</v>
       </c>
       <c r="D41" t="n">
         <v>2026</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
         <v>2026</v>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1960</v>
+        <v>2479</v>
       </c>
       <c r="D45" t="n">
         <v>2026</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D46" t="n">
         <v>2026</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="D47" t="n">
         <v>2026</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D48" t="n">
         <v>2026</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="D49" t="n">
         <v>2026</v>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>517</v>
+        <v>392</v>
       </c>
       <c r="D50" t="n">
         <v>2026</v>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1551</v>
+        <v>1176</v>
       </c>
       <c r="D51" t="n">
         <v>2026</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>2026</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1220</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>2026</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="D54" t="n">
         <v>2026</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1414</v>
+        <v>2971</v>
       </c>
       <c r="D55" t="n">
         <v>2026</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D56" t="n">
         <v>2026</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D57" t="n">
         <v>2026</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D58" t="n">
         <v>2026</v>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D59" t="n">
         <v>2026</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D60" t="n">
         <v>2026</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D61" t="n">
         <v>2026</v>
